--- a/Teoría de la información/Notas del día/Día 8.xlsx
+++ b/Teoría de la información/Notas del día/Día 8.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositories\Semestre-EneJun2026\Teoría de la información\Notas del día\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{408FD894-36E4-48E7-AE09-81DD4FADFA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{877FD313-966B-42BF-A61B-28F5816BE428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F60DBD52-30DC-4A43-8218-4A6BBC7AAA2F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="25">
   <si>
     <t>Contamos cuántas veces aparece cada letra</t>
   </si>
@@ -507,23 +507,74 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EE551B6-C548-4998-9C3A-241940C22CC2}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" t="s">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>13</v>
+      </c>
+      <c r="R4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" t="s">
+        <v>5</v>
+      </c>
+      <c r="T4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" t="s">
+        <v>15</v>
+      </c>
+      <c r="V4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -537,7 +588,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -545,14 +596,17 @@
         <v>1</v>
       </c>
       <c r="C6" s="4">
-        <f>B6 / $B$23</f>
+        <f t="shared" ref="C6:C22" si="0">B6 / $B$23</f>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -560,7 +614,7 @@
         <v>6</v>
       </c>
       <c r="C7" s="4">
-        <f>B7 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>0.13333333333333333</v>
       </c>
       <c r="D7" s="5"/>
@@ -568,7 +622,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -576,12 +630,12 @@
         <v>1</v>
       </c>
       <c r="C8" s="4">
-        <f>B8 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="D8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -589,12 +643,12 @@
         <v>2</v>
       </c>
       <c r="C9" s="4">
-        <f>B9 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -602,12 +656,12 @@
         <v>3</v>
       </c>
       <c r="C10" s="4">
-        <f>B10 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -615,12 +669,12 @@
         <v>5</v>
       </c>
       <c r="C11" s="4">
-        <f>B11 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="D11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -628,12 +682,12 @@
         <v>1</v>
       </c>
       <c r="C12" s="4">
-        <f>B12 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -641,12 +695,12 @@
         <v>4</v>
       </c>
       <c r="C13" s="4">
-        <f>B13 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="D13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -654,12 +708,12 @@
         <v>2</v>
       </c>
       <c r="C14" s="4">
-        <f>B14 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -667,12 +721,12 @@
         <v>1</v>
       </c>
       <c r="C15" s="4">
-        <f>B15 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="D15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -680,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="4">
-        <f>B16 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D16" s="5"/>
@@ -693,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C17" s="4">
-        <f>B17 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>6.6666666666666666E-2</v>
       </c>
       <c r="D17" s="5"/>
@@ -706,7 +760,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="4">
-        <f>B18 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>4.4444444444444446E-2</v>
       </c>
       <c r="D18" s="5"/>
@@ -719,7 +773,7 @@
         <v>4</v>
       </c>
       <c r="C19" s="4">
-        <f>B19 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>8.8888888888888892E-2</v>
       </c>
       <c r="D19" s="5"/>
@@ -732,7 +786,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="4">
-        <f>B20 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="D20" s="5"/>
@@ -745,7 +799,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="4">
-        <f>B21 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="D21" s="5"/>
@@ -758,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="4">
-        <f>B22 / $B$23</f>
+        <f t="shared" si="0"/>
         <v>2.2222222222222223E-2</v>
       </c>
       <c r="D22" s="5"/>
